--- a/VerveStacks_VEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_VEN_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_VEN_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA85ADF3-C085-4CB3-AF67-B373E15D2FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{075EFC78-D895-4E67-A797-580150609F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3418" uniqueCount="763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="760">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -2404,15 +2404,6 @@
   </si>
   <si>
     <t>STG</t>
-  </si>
-  <si>
-    <t>Trd_electricity import</t>
-  </si>
-  <si>
-    <t>e_VE1-230,e_VE10-230,e_VE11-230,e_VE12-230,e_VE13-230,e_VE2-230,e_VE24-230,e_VE25-230,e_VE3-230,e_VE4-230,e_VE4-400,e_VE5-230,e_VE5-400,e_VE52-230,e_VE58-230,e_VE59-230,e_VE6-230,e_VE8-230,e_VE9-230,e_w187936908-230,e_w187936908-400,e_w264134612-230,e_w264134612-400,e_w264156840-230,e_w264156841-230,e_w264156842-230,e_w265064743-400,e_w365007880-230,e_w365007880-400,e_w502761909-230,e_w565534382-230,e_w609494059-230,e_w677150278-230,e_w794639093-230,e_w798451066-230,e_w801987822-230</t>
-  </si>
-  <si>
-    <t>Trd_electricity export</t>
   </si>
 </sst>
 </file>
@@ -3612,10 +3603,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A293467C-F587-42A9-A6B4-3EFC8DBA0027}">
-  <dimension ref="B2:AJ366"/>
+  <dimension ref="B2:AF366"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -3628,11 +3619,8 @@
       <c r="U2" t="s">
         <v>340</v>
       </c>
-      <c r="AH2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="3" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>3</v>
       </c>
@@ -3684,17 +3672,8 @@
       <c r="AA3" t="s">
         <v>262</v>
       </c>
-      <c r="AH3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>263</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="4" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>95</v>
       </c>
@@ -3761,17 +3740,8 @@
       <c r="AF4" t="s">
         <v>757</v>
       </c>
-      <c r="AH4" t="s">
-        <v>760</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>761</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="5" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>96</v>
       </c>
@@ -3835,17 +3805,8 @@
       <c r="AF5" t="s">
         <v>758</v>
       </c>
-      <c r="AH5" t="s">
-        <v>762</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>761</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="6" spans="2:36" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
         <v>97</v>
       </c>
@@ -3910,7 +3871,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="7" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>98</v>
       </c>
@@ -3960,7 +3921,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="8" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>99</v>
       </c>
@@ -4010,7 +3971,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="9" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>100</v>
       </c>
@@ -4060,7 +4021,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="10" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>101</v>
       </c>
@@ -4110,7 +4071,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="11" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>102</v>
       </c>
@@ -4160,7 +4121,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="12" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>103</v>
       </c>
@@ -4210,7 +4171,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>104</v>
       </c>
@@ -4260,7 +4221,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>105</v>
       </c>
@@ -4310,7 +4271,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="15" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>106</v>
       </c>
@@ -4360,7 +4321,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="2:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:32" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>107</v>
       </c>
